--- a/Chat-Conversations-Implementation-Plan.xlsx
+++ b/Chat-Conversations-Implementation-Plan.xlsx
@@ -1130,7 +1130,7 @@
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
